--- a/docs/models.xlsx
+++ b/docs/models.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
+          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180', '6.2': '6.2-4.4.59'}</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -458,7 +458,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
+          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180', '6.2': '6.2-3.10.105'}</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
+          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180', '6.2': '6.2-4.4.59'}</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
+          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180', '6.2': '6.2-4.4.59'}</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
+          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180', '6.2': '6.2-4.4.59'}</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
+          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180', '6.2': '6.2-4.4.59'}</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
+          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180', '6.2': '6.2-4.4.59'}</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>['DS725+', 'DS725neo+']</t>
+          <t>['DS725neo+', 'DS725+']</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>['DS1525+', 'DS1525neo+', 'DS1825+', 'DS1825neo+', 'DS925+', 'DS925neo+', 'DVA7400', 'RS1226+', 'RS1226RP+', 'RS2423RP+II', 'RS2825RP+', 'RS826+', 'RS826RP+']</t>
+          <t>['DS1525neo+', 'DS1825neo+', 'DS925neo+', 'DS1525+', 'DS1825+', 'DS925+', 'DVA7400', 'RS1226+', 'RS1226RP+', 'RS2423RP+II', 'RS2825RP+', 'RS826+', 'RS826RP+']</t>
         </is>
       </c>
     </row>
